--- a/00 Raw data/研究量能統計 2017-2025.xlsx
+++ b/00 Raw data/研究量能統計 2017-2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8C9652-1216-4134-BFED-F26DA5722185}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACD25F0-4153-4135-8982-5C7708C1059D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -345,9 +345,6 @@
     <t>General (ASJC)</t>
   </si>
   <si>
-    <t>2026.07.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">大專校院資訊公開平台
 https://udb.moe.edu.tw/udata/DetailReportList/%E6%95%99%E8%81%B7%E9%A1%9E/StatUniversityRegularTeacher/Index </t>
   </si>
@@ -527,6 +524,9 @@
   <si>
     <t>YUNTECH</t>
   </si>
+  <si>
+    <t>2026.08.05</t>
+  </si>
 </sst>
 </file>
 
@@ -667,7 +667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -758,9 +758,6 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -770,15 +767,19 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -841,6 +842,60 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD81EDAE-8275-4840-A988-57F75B98870B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -1058,25 +1113,25 @@
     <col min="1" max="1" width="8.8984375" style="5" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.8984375" style="26" customWidth="1"/>
-    <col min="4" max="4" width="16.69921875" style="33" customWidth="1"/>
+    <col min="4" max="4" width="16.69921875" style="32" customWidth="1"/>
     <col min="5" max="5" width="12.8984375" style="14" customWidth="1"/>
     <col min="6" max="6" width="17" style="19" customWidth="1"/>
     <col min="7" max="7" width="18.796875" style="19" customWidth="1"/>
-    <col min="8" max="8" width="12.19921875" style="33" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" style="33" customWidth="1"/>
-    <col min="10" max="10" width="20.8984375" style="33" customWidth="1"/>
-    <col min="11" max="11" width="19" style="35" customWidth="1"/>
+    <col min="8" max="8" width="12.19921875" style="32" customWidth="1"/>
+    <col min="9" max="9" width="9.19921875" style="32" customWidth="1"/>
+    <col min="10" max="10" width="20.8984375" style="32" customWidth="1"/>
+    <col min="11" max="11" width="19" style="34" customWidth="1"/>
     <col min="12" max="12" width="21.3984375" style="28" customWidth="1"/>
-    <col min="13" max="13" width="23.09765625" style="33" customWidth="1"/>
-    <col min="14" max="14" width="20.8984375" style="33" customWidth="1"/>
-    <col min="15" max="15" width="19" style="35" customWidth="1"/>
+    <col min="13" max="13" width="23.09765625" style="32" customWidth="1"/>
+    <col min="14" max="14" width="20.8984375" style="32" customWidth="1"/>
+    <col min="15" max="15" width="19" style="34" customWidth="1"/>
     <col min="16" max="16" width="21.3984375" style="28" customWidth="1"/>
-    <col min="17" max="17" width="23.09765625" style="33" customWidth="1"/>
-    <col min="18" max="18" width="20.8984375" style="33" customWidth="1"/>
-    <col min="19" max="19" width="17" style="35" customWidth="1"/>
+    <col min="17" max="17" width="23.09765625" style="32" customWidth="1"/>
+    <col min="18" max="18" width="20.8984375" style="32" customWidth="1"/>
+    <col min="19" max="19" width="17" style="34" customWidth="1"/>
     <col min="20" max="20" width="19.296875" style="28" customWidth="1"/>
-    <col min="21" max="21" width="25" style="33" customWidth="1"/>
-    <col min="22" max="22" width="21.09765625" style="35" customWidth="1"/>
+    <col min="21" max="21" width="25" style="32" customWidth="1"/>
+    <col min="22" max="22" width="21.09765625" style="34" customWidth="1"/>
     <col min="23" max="23" width="23.3984375" style="28" customWidth="1"/>
     <col min="24" max="16384" width="8.8984375" style="5"/>
   </cols>
@@ -1091,7 +1146,7 @@
       <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="12" t="s">
@@ -1103,49 +1158,49 @@
       <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="34" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="O1" s="34" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="Q1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="S1" s="34" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="33" t="s">
+      <c r="U1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="35" t="s">
+      <c r="V1" s="34" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="30" t="s">
@@ -1188,6 +1243,9 @@
       <c r="K2" s="24">
         <v>277</v>
       </c>
+      <c r="L2" s="39">
+        <v>1.68</v>
+      </c>
       <c r="M2" s="24">
         <v>46.2</v>
       </c>
@@ -1197,20 +1255,29 @@
       <c r="O2" s="24">
         <v>24</v>
       </c>
+      <c r="P2" s="39">
+        <v>1.01</v>
+      </c>
       <c r="Q2" s="24">
         <v>24.2</v>
       </c>
       <c r="R2" s="24">
         <v>12.3</v>
       </c>
-      <c r="S2" s="38">
+      <c r="S2" s="36">
         <v>143</v>
       </c>
-      <c r="U2" s="38">
+      <c r="T2" s="39">
+        <v>4.34</v>
+      </c>
+      <c r="U2" s="36">
         <v>32</v>
       </c>
-      <c r="V2" s="38">
+      <c r="V2" s="36">
         <v>262</v>
+      </c>
+      <c r="W2" s="39">
+        <v>1.98</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -1249,7 +1316,7 @@
       <c r="K3" s="24">
         <v>388</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="39">
         <v>1.25</v>
       </c>
       <c r="M3" s="24">
@@ -1261,7 +1328,7 @@
       <c r="O3" s="24">
         <v>35</v>
       </c>
-      <c r="P3" s="29">
+      <c r="P3" s="39">
         <v>0.67</v>
       </c>
       <c r="Q3" s="24">
@@ -1273,7 +1340,7 @@
       <c r="S3" s="24">
         <v>146</v>
       </c>
-      <c r="T3" s="29">
+      <c r="T3" s="39">
         <v>4.18</v>
       </c>
       <c r="U3" s="24">
@@ -1282,7 +1349,7 @@
       <c r="V3" s="24">
         <v>279</v>
       </c>
-      <c r="W3" s="29">
+      <c r="W3" s="39">
         <v>1.77</v>
       </c>
     </row>
@@ -1322,7 +1389,7 @@
       <c r="K4" s="24">
         <v>426</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="39">
         <v>1.48</v>
       </c>
       <c r="M4" s="24">
@@ -1334,7 +1401,7 @@
       <c r="O4" s="24">
         <v>36</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="39">
         <v>0.76</v>
       </c>
       <c r="Q4" s="24">
@@ -1346,7 +1413,7 @@
       <c r="S4" s="24">
         <v>180</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="39">
         <v>4.2</v>
       </c>
       <c r="U4" s="24">
@@ -1355,7 +1422,7 @@
       <c r="V4" s="24">
         <v>317</v>
       </c>
-      <c r="W4" s="29">
+      <c r="W4" s="39">
         <v>2.17</v>
       </c>
     </row>
@@ -1395,7 +1462,7 @@
       <c r="K5" s="24">
         <v>498</v>
       </c>
-      <c r="L5" s="29">
+      <c r="L5" s="39">
         <v>1.39</v>
       </c>
       <c r="M5" s="24">
@@ -1407,8 +1474,8 @@
       <c r="O5" s="24">
         <v>41</v>
       </c>
-      <c r="P5" s="29">
-        <v>0.97</v>
+      <c r="P5" s="39">
+        <v>0.99</v>
       </c>
       <c r="Q5" s="24">
         <v>22.5</v>
@@ -1419,8 +1486,8 @@
       <c r="S5" s="24">
         <v>211</v>
       </c>
-      <c r="T5" s="29">
-        <v>4.34</v>
+      <c r="T5" s="39">
+        <v>4.3899999999999997</v>
       </c>
       <c r="U5" s="24">
         <v>35.200000000000003</v>
@@ -1428,8 +1495,8 @@
       <c r="V5" s="24">
         <v>408</v>
       </c>
-      <c r="W5" s="29">
-        <v>1.75</v>
+      <c r="W5" s="39">
+        <v>1.77</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -1468,7 +1535,7 @@
       <c r="K6" s="24">
         <v>572</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="39">
         <v>1.29</v>
       </c>
       <c r="M6" s="24">
@@ -1480,7 +1547,7 @@
       <c r="O6" s="24">
         <v>42</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="39">
         <v>1.0900000000000001</v>
       </c>
       <c r="Q6" s="24">
@@ -1492,7 +1559,7 @@
       <c r="S6" s="24">
         <v>222</v>
       </c>
-      <c r="T6" s="29">
+      <c r="T6" s="39">
         <v>3.6</v>
       </c>
       <c r="U6" s="24">
@@ -1501,7 +1568,7 @@
       <c r="V6" s="24">
         <v>387</v>
       </c>
-      <c r="W6" s="29">
+      <c r="W6" s="39">
         <v>1.61</v>
       </c>
     </row>
@@ -1540,7 +1607,7 @@
       <c r="K7" s="24">
         <v>671</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="39">
         <v>1.29</v>
       </c>
       <c r="M7" s="24">
@@ -1552,7 +1619,7 @@
       <c r="O7" s="24">
         <v>74</v>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="39">
         <v>1.2</v>
       </c>
       <c r="Q7" s="24">
@@ -1564,7 +1631,7 @@
       <c r="S7" s="24">
         <v>251</v>
       </c>
-      <c r="T7" s="29">
+      <c r="T7" s="39">
         <v>3.98</v>
       </c>
       <c r="U7" s="24">
@@ -1573,7 +1640,7 @@
       <c r="V7" s="24">
         <v>444</v>
       </c>
-      <c r="W7" s="29">
+      <c r="W7" s="39">
         <v>1.53</v>
       </c>
     </row>
@@ -1613,8 +1680,8 @@
       <c r="K8" s="24">
         <v>605</v>
       </c>
-      <c r="L8" s="29">
-        <v>1.41</v>
+      <c r="L8" s="39">
+        <v>1.4</v>
       </c>
       <c r="M8" s="24">
         <v>18.7</v>
@@ -1625,8 +1692,8 @@
       <c r="O8" s="24">
         <v>37</v>
       </c>
-      <c r="P8" s="29">
-        <v>1.07</v>
+      <c r="P8" s="39">
+        <v>1.08</v>
       </c>
       <c r="Q8" s="24">
         <v>15.8</v>
@@ -1637,8 +1704,8 @@
       <c r="S8" s="24">
         <v>275</v>
       </c>
-      <c r="T8" s="29">
-        <v>4.03</v>
+      <c r="T8" s="39">
+        <v>4.04</v>
       </c>
       <c r="U8" s="24">
         <v>33.200000000000003</v>
@@ -1646,8 +1713,8 @@
       <c r="V8" s="24">
         <v>394</v>
       </c>
-      <c r="W8" s="29">
-        <v>1.75</v>
+      <c r="W8" s="39">
+        <v>1.74</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -1686,7 +1753,7 @@
       <c r="K9" s="24">
         <v>665</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="39">
         <v>1.46</v>
       </c>
       <c r="M9" s="24">
@@ -1698,8 +1765,8 @@
       <c r="O9" s="24">
         <v>41</v>
       </c>
-      <c r="P9" s="29">
-        <v>1.04</v>
+      <c r="P9" s="39">
+        <v>1.03</v>
       </c>
       <c r="Q9" s="24">
         <v>11.9</v>
@@ -1710,8 +1777,8 @@
       <c r="S9" s="24">
         <v>303</v>
       </c>
-      <c r="T9" s="29">
-        <v>4.09</v>
+      <c r="T9" s="39">
+        <v>4</v>
       </c>
       <c r="U9" s="24">
         <v>38</v>
@@ -1719,8 +1786,8 @@
       <c r="V9" s="24">
         <v>493</v>
       </c>
-      <c r="W9" s="29">
-        <v>1.7</v>
+      <c r="W9" s="39">
+        <v>1.69</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -1759,8 +1826,8 @@
       <c r="K10" s="24">
         <v>737</v>
       </c>
-      <c r="L10" s="29">
-        <v>1.48</v>
+      <c r="L10" s="39">
+        <v>1.46</v>
       </c>
       <c r="M10" s="24">
         <v>6.8</v>
@@ -1771,8 +1838,8 @@
       <c r="O10" s="24">
         <v>43</v>
       </c>
-      <c r="P10" s="29">
-        <v>1.27</v>
+      <c r="P10" s="39">
+        <v>1.24</v>
       </c>
       <c r="Q10" s="24">
         <v>4.2</v>
@@ -1783,8 +1850,8 @@
       <c r="S10" s="24">
         <v>403</v>
       </c>
-      <c r="T10" s="29">
-        <v>7.43</v>
+      <c r="T10" s="39">
+        <v>7.51</v>
       </c>
       <c r="U10" s="24">
         <v>43</v>
@@ -1792,8 +1859,8 @@
       <c r="V10" s="24">
         <v>654</v>
       </c>
-      <c r="W10" s="29">
-        <v>1.7</v>
+      <c r="W10" s="39">
+        <v>1.68</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -1824,8 +1891,8 @@
       <c r="K11" s="24">
         <v>4839</v>
       </c>
-      <c r="L11" s="29">
-        <v>1.39</v>
+      <c r="L11" s="39">
+        <v>1.4</v>
       </c>
       <c r="M11" s="24">
         <v>23.9</v>
@@ -1836,7 +1903,7 @@
       <c r="O11" s="24">
         <v>373</v>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="39">
         <v>1.04</v>
       </c>
       <c r="Q11" s="24">
@@ -1848,8 +1915,8 @@
       <c r="S11" s="24">
         <v>2134</v>
       </c>
-      <c r="T11" s="29">
-        <v>4.62</v>
+      <c r="T11" s="39">
+        <v>4.58</v>
       </c>
       <c r="U11" s="24">
         <v>34.799999999999997</v>
@@ -1857,8 +1924,8 @@
       <c r="V11" s="24">
         <v>3638</v>
       </c>
-      <c r="W11" s="29">
-        <v>1.73</v>
+      <c r="W11" s="39">
+        <v>1.74</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -1896,13 +1963,13 @@
       <c r="R12" s="24">
         <v>10.4</v>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="36">
         <v>4000</v>
       </c>
-      <c r="U12" s="38">
+      <c r="U12" s="36">
         <v>33.9</v>
       </c>
-      <c r="V12" s="38">
+      <c r="V12" s="36">
         <v>10354</v>
       </c>
     </row>
@@ -1919,7 +1986,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
-      <c r="H13" s="37"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="24">
         <v>1.0900000000000001</v>
       </c>
@@ -1979,7 +2046,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="34"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="24">
         <v>1.1200000000000001</v>
       </c>
@@ -2039,7 +2106,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
-      <c r="H15" s="34"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="24">
         <v>1.2</v>
       </c>
@@ -2099,7 +2166,7 @@
       <c r="E16" s="19"/>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
-      <c r="H16" s="34"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="24">
         <v>1.1499999999999999</v>
       </c>
@@ -2159,7 +2226,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
-      <c r="H17" s="34"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="24">
         <v>1.2</v>
       </c>
@@ -2219,7 +2286,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="34"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="24">
         <v>1.22</v>
       </c>
@@ -2279,7 +2346,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
-      <c r="H19" s="34"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="24">
         <v>1.27</v>
       </c>
@@ -2337,7 +2404,7 @@
         <v>49813</v>
       </c>
       <c r="E20" s="19"/>
-      <c r="H20" s="34"/>
+      <c r="H20" s="33"/>
       <c r="I20" s="24">
         <v>1.25</v>
       </c>
@@ -2397,7 +2464,7 @@
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
-      <c r="H21" s="34"/>
+      <c r="H21" s="33"/>
       <c r="I21" s="24">
         <v>1.18</v>
       </c>
@@ -2480,6 +2547,9 @@
       <c r="K22" s="24">
         <v>35</v>
       </c>
+      <c r="L22" s="39">
+        <v>1.63</v>
+      </c>
       <c r="M22" s="24">
         <v>37.700000000000003</v>
       </c>
@@ -2489,6 +2559,9 @@
       <c r="O22" s="24">
         <v>1</v>
       </c>
+      <c r="P22" s="39">
+        <v>0.26</v>
+      </c>
       <c r="Q22" s="24">
         <v>10</v>
       </c>
@@ -2498,11 +2571,17 @@
       <c r="S22" s="24">
         <v>14</v>
       </c>
-      <c r="U22" s="38">
+      <c r="T22" s="39">
+        <v>5.81</v>
+      </c>
+      <c r="U22" s="36">
         <v>19.3</v>
       </c>
-      <c r="V22" s="38">
+      <c r="V22" s="36">
         <v>35</v>
+      </c>
+      <c r="W22" s="39">
+        <v>1.81</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2541,7 +2620,7 @@
       <c r="K23" s="24">
         <v>33</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="39">
         <v>0.54</v>
       </c>
       <c r="M23" s="24">
@@ -2553,7 +2632,7 @@
       <c r="O23" s="24">
         <v>0</v>
       </c>
-      <c r="P23" s="29" t="s">
+      <c r="P23" s="39" t="s">
         <v>36</v>
       </c>
       <c r="Q23" s="24" t="s">
@@ -2565,7 +2644,7 @@
       <c r="S23" s="24">
         <v>15</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="39">
         <v>4.13</v>
       </c>
       <c r="U23" s="24">
@@ -2574,7 +2653,7 @@
       <c r="V23" s="24">
         <v>22</v>
       </c>
-      <c r="W23" s="29">
+      <c r="W23" s="39">
         <v>1.58</v>
       </c>
     </row>
@@ -2614,7 +2693,7 @@
       <c r="K24" s="24">
         <v>40</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="39">
         <v>0.52</v>
       </c>
       <c r="M24" s="24">
@@ -2626,7 +2705,7 @@
       <c r="O24" s="24">
         <v>2</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="39">
         <v>0.1</v>
       </c>
       <c r="Q24" s="24">
@@ -2638,7 +2717,7 @@
       <c r="S24" s="24">
         <v>10</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="39">
         <v>3.57</v>
       </c>
       <c r="U24" s="24">
@@ -2647,7 +2726,7 @@
       <c r="V24" s="24">
         <v>25</v>
       </c>
-      <c r="W24" s="29">
+      <c r="W24" s="39">
         <v>1.18</v>
       </c>
     </row>
@@ -2687,7 +2766,7 @@
       <c r="K25" s="24">
         <v>53</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="39">
         <v>0.63</v>
       </c>
       <c r="M25" s="24">
@@ -2699,7 +2778,7 @@
       <c r="O25" s="24">
         <v>1</v>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="39">
         <v>0.04</v>
       </c>
       <c r="Q25" s="24">
@@ -2711,7 +2790,7 @@
       <c r="S25" s="24">
         <v>14</v>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="39">
         <v>3.77</v>
       </c>
       <c r="U25" s="24">
@@ -2720,7 +2799,7 @@
       <c r="V25" s="24">
         <v>31</v>
       </c>
-      <c r="W25" s="29">
+      <c r="W25" s="39">
         <v>1.1599999999999999</v>
       </c>
     </row>
@@ -2760,7 +2839,7 @@
       <c r="K26" s="24">
         <v>43</v>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="39">
         <v>1.76</v>
       </c>
       <c r="M26" s="24">
@@ -2772,7 +2851,7 @@
       <c r="O26" s="24">
         <v>4</v>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="39">
         <v>6.28</v>
       </c>
       <c r="Q26" s="24">
@@ -2784,7 +2863,7 @@
       <c r="S26" s="24">
         <v>10</v>
       </c>
-      <c r="T26" s="29">
+      <c r="T26" s="39">
         <v>7.8</v>
       </c>
       <c r="U26" s="24">
@@ -2793,7 +2872,7 @@
       <c r="V26" s="24">
         <v>30</v>
       </c>
-      <c r="W26" s="29">
+      <c r="W26" s="39">
         <v>1.18</v>
       </c>
     </row>
@@ -2833,7 +2912,7 @@
       <c r="K27" s="24">
         <v>52</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="39">
         <v>0.96</v>
       </c>
       <c r="M27" s="24">
@@ -2845,7 +2924,7 @@
       <c r="O27" s="24">
         <v>4</v>
       </c>
-      <c r="P27" s="29">
+      <c r="P27" s="39">
         <v>0.87</v>
       </c>
       <c r="Q27" s="24">
@@ -2857,7 +2936,7 @@
       <c r="S27" s="24">
         <v>19</v>
       </c>
-      <c r="T27" s="29">
+      <c r="T27" s="39">
         <v>4.5999999999999996</v>
       </c>
       <c r="U27" s="24">
@@ -2866,7 +2945,7 @@
       <c r="V27" s="24">
         <v>39</v>
       </c>
-      <c r="W27" s="29">
+      <c r="W27" s="39">
         <v>0.97</v>
       </c>
     </row>
@@ -2906,8 +2985,8 @@
       <c r="K28" s="24">
         <v>48</v>
       </c>
-      <c r="L28" s="29">
-        <v>0.85</v>
+      <c r="L28" s="39">
+        <v>0.84</v>
       </c>
       <c r="M28" s="24">
         <v>9.4</v>
@@ -2918,8 +2997,8 @@
       <c r="O28" s="24">
         <v>11</v>
       </c>
-      <c r="P28" s="29">
-        <v>0.57999999999999996</v>
+      <c r="P28" s="39">
+        <v>0.59</v>
       </c>
       <c r="Q28" s="24">
         <v>6.7</v>
@@ -2930,8 +3009,8 @@
       <c r="S28" s="24">
         <v>12</v>
       </c>
-      <c r="T28" s="29">
-        <v>3.45</v>
+      <c r="T28" s="39">
+        <v>3.49</v>
       </c>
       <c r="U28" s="24">
         <v>16.899999999999999</v>
@@ -2939,8 +3018,8 @@
       <c r="V28" s="24">
         <v>37</v>
       </c>
-      <c r="W28" s="29">
-        <v>1.1299999999999999</v>
+      <c r="W28" s="39">
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -2979,7 +3058,7 @@
       <c r="K29" s="24">
         <v>56</v>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="39">
         <v>0.75</v>
       </c>
       <c r="M29" s="24">
@@ -2991,8 +3070,8 @@
       <c r="O29" s="24">
         <v>10</v>
       </c>
-      <c r="P29" s="29">
-        <v>0.82</v>
+      <c r="P29" s="39">
+        <v>0.92</v>
       </c>
       <c r="Q29" s="24">
         <v>8.5</v>
@@ -3003,8 +3082,8 @@
       <c r="S29" s="24">
         <v>16</v>
       </c>
-      <c r="T29" s="29">
-        <v>3.75</v>
+      <c r="T29" s="39">
+        <v>3.63</v>
       </c>
       <c r="U29" s="24">
         <v>19.399999999999999</v>
@@ -3012,7 +3091,7 @@
       <c r="V29" s="24">
         <v>44</v>
       </c>
-      <c r="W29" s="29">
+      <c r="W29" s="39">
         <v>1.23</v>
       </c>
     </row>
@@ -3052,8 +3131,8 @@
       <c r="K30" s="24">
         <v>86</v>
       </c>
-      <c r="L30" s="29">
-        <v>0.93</v>
+      <c r="L30" s="39">
+        <v>0.92</v>
       </c>
       <c r="M30" s="24">
         <v>2.5</v>
@@ -3064,8 +3143,8 @@
       <c r="O30" s="24">
         <v>8</v>
       </c>
-      <c r="P30" s="29">
-        <v>0.55000000000000004</v>
+      <c r="P30" s="39">
+        <v>0.53</v>
       </c>
       <c r="Q30" s="24">
         <v>2.6</v>
@@ -3076,8 +3155,8 @@
       <c r="S30" s="24">
         <v>29</v>
       </c>
-      <c r="T30" s="29">
-        <v>4.83</v>
+      <c r="T30" s="39">
+        <v>4.9000000000000004</v>
       </c>
       <c r="U30" s="24">
         <v>20.6</v>
@@ -3085,8 +3164,8 @@
       <c r="V30" s="24">
         <v>64</v>
       </c>
-      <c r="W30" s="29">
-        <v>1.03</v>
+      <c r="W30" s="39">
+        <v>1.06</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3117,8 +3196,8 @@
       <c r="K31" s="24">
         <v>446</v>
       </c>
-      <c r="L31" s="29">
-        <v>0.88</v>
+      <c r="L31" s="39">
+        <v>0.93</v>
       </c>
       <c r="M31" s="24">
         <v>13.4</v>
@@ -3129,7 +3208,7 @@
       <c r="O31" s="24">
         <v>41</v>
       </c>
-      <c r="P31" s="29">
+      <c r="P31" s="39">
         <v>1.2</v>
       </c>
       <c r="Q31" s="24">
@@ -3141,8 +3220,8 @@
       <c r="S31" s="24">
         <v>139</v>
       </c>
-      <c r="T31" s="29">
-        <v>4.49</v>
+      <c r="T31" s="39">
+        <v>4.5999999999999996</v>
       </c>
       <c r="U31" s="24">
         <v>17.100000000000001</v>
@@ -3150,8 +3229,8 @@
       <c r="V31" s="24">
         <v>327</v>
       </c>
-      <c r="W31" s="29">
-        <v>1.1499999999999999</v>
+      <c r="W31" s="39">
+        <v>1.22</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3190,6 +3269,9 @@
       <c r="K32" s="24">
         <v>59</v>
       </c>
+      <c r="L32" s="39">
+        <v>0.77</v>
+      </c>
       <c r="M32" s="24">
         <v>27.3</v>
       </c>
@@ -3199,20 +3281,29 @@
       <c r="O32" s="24">
         <v>3</v>
       </c>
+      <c r="P32" s="39">
+        <v>0.95</v>
+      </c>
       <c r="Q32" s="24">
         <v>18.3</v>
       </c>
       <c r="R32" s="24">
         <v>9.4</v>
       </c>
-      <c r="S32" s="38">
+      <c r="S32" s="36">
         <v>25</v>
       </c>
-      <c r="U32" s="38">
+      <c r="T32" s="39">
+        <v>3.94</v>
+      </c>
+      <c r="U32" s="36">
         <v>23.9</v>
       </c>
-      <c r="V32" s="38">
+      <c r="V32" s="36">
         <v>57</v>
+      </c>
+      <c r="W32" s="39">
+        <v>1.4</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3251,7 +3342,7 @@
       <c r="K33" s="24">
         <v>76</v>
       </c>
-      <c r="L33" s="29">
+      <c r="L33" s="39">
         <v>0.87</v>
       </c>
       <c r="M33" s="24">
@@ -3263,7 +3354,7 @@
       <c r="O33" s="24">
         <v>5</v>
       </c>
-      <c r="P33" s="29">
+      <c r="P33" s="39">
         <v>0.22</v>
       </c>
       <c r="Q33" s="24">
@@ -3275,7 +3366,7 @@
       <c r="S33" s="24">
         <v>31</v>
       </c>
-      <c r="T33" s="29">
+      <c r="T33" s="39">
         <v>3.67</v>
       </c>
       <c r="U33" s="24">
@@ -3284,7 +3375,7 @@
       <c r="V33" s="24">
         <v>51</v>
       </c>
-      <c r="W33" s="29">
+      <c r="W33" s="39">
         <v>1.38</v>
       </c>
     </row>
@@ -3324,7 +3415,7 @@
       <c r="K34" s="24">
         <v>110</v>
       </c>
-      <c r="L34" s="29">
+      <c r="L34" s="39">
         <v>1.21</v>
       </c>
       <c r="M34" s="24">
@@ -3336,7 +3427,7 @@
       <c r="O34" s="24">
         <v>1</v>
       </c>
-      <c r="P34" s="29">
+      <c r="P34" s="39">
         <v>0</v>
       </c>
       <c r="Q34" s="24" t="s">
@@ -3348,7 +3439,7 @@
       <c r="S34" s="24">
         <v>43</v>
       </c>
-      <c r="T34" s="29">
+      <c r="T34" s="39">
         <v>4.29</v>
       </c>
       <c r="U34" s="24">
@@ -3357,7 +3448,7 @@
       <c r="V34" s="24">
         <v>61</v>
       </c>
-      <c r="W34" s="29">
+      <c r="W34" s="39">
         <v>1.66</v>
       </c>
     </row>
@@ -3397,7 +3488,7 @@
       <c r="K35" s="24">
         <v>115</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="39">
         <v>0.99</v>
       </c>
       <c r="M35" s="24">
@@ -3409,7 +3500,7 @@
       <c r="O35" s="24">
         <v>0</v>
       </c>
-      <c r="P35" s="29" t="s">
+      <c r="P35" s="39" t="s">
         <v>36</v>
       </c>
       <c r="Q35" s="24" t="s">
@@ -3421,8 +3512,8 @@
       <c r="S35" s="24">
         <v>38</v>
       </c>
-      <c r="T35" s="29">
-        <v>4.79</v>
+      <c r="T35" s="39">
+        <v>4.8</v>
       </c>
       <c r="U35" s="24">
         <v>23.7</v>
@@ -3430,7 +3521,7 @@
       <c r="V35" s="24">
         <v>77</v>
       </c>
-      <c r="W35" s="29">
+      <c r="W35" s="39">
         <v>1.57</v>
       </c>
     </row>
@@ -3470,7 +3561,7 @@
       <c r="K36" s="24">
         <v>167</v>
       </c>
-      <c r="L36" s="29">
+      <c r="L36" s="39">
         <v>0.98</v>
       </c>
       <c r="M36" s="24">
@@ -3482,7 +3573,7 @@
       <c r="O36" s="24">
         <v>4</v>
       </c>
-      <c r="P36" s="29">
+      <c r="P36" s="39">
         <v>0.51</v>
       </c>
       <c r="Q36" s="24">
@@ -3494,7 +3585,7 @@
       <c r="S36" s="24">
         <v>52</v>
       </c>
-      <c r="T36" s="29">
+      <c r="T36" s="39">
         <v>3.26</v>
       </c>
       <c r="U36" s="24">
@@ -3503,7 +3594,7 @@
       <c r="V36" s="24">
         <v>90</v>
       </c>
-      <c r="W36" s="29">
+      <c r="W36" s="39">
         <v>1.5</v>
       </c>
     </row>
@@ -3543,7 +3634,7 @@
       <c r="K37" s="24">
         <v>197</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="39">
         <v>1.1100000000000001</v>
       </c>
       <c r="M37" s="24">
@@ -3555,7 +3646,7 @@
       <c r="O37" s="24">
         <v>5</v>
       </c>
-      <c r="P37" s="29">
+      <c r="P37" s="39">
         <v>0.99</v>
       </c>
       <c r="Q37" s="24">
@@ -3567,7 +3658,7 @@
       <c r="S37" s="24">
         <v>60</v>
       </c>
-      <c r="T37" s="29">
+      <c r="T37" s="39">
         <v>3.74</v>
       </c>
       <c r="U37" s="24">
@@ -3576,7 +3667,7 @@
       <c r="V37" s="24">
         <v>95</v>
       </c>
-      <c r="W37" s="29">
+      <c r="W37" s="39">
         <v>1.63</v>
       </c>
     </row>
@@ -3616,8 +3707,8 @@
       <c r="K38" s="24">
         <v>177</v>
       </c>
-      <c r="L38" s="29">
-        <v>1.07</v>
+      <c r="L38" s="39">
+        <v>1.06</v>
       </c>
       <c r="M38" s="24">
         <v>12.5</v>
@@ -3628,8 +3719,8 @@
       <c r="O38" s="24">
         <v>2</v>
       </c>
-      <c r="P38" s="29">
-        <v>1.25</v>
+      <c r="P38" s="39">
+        <v>1.22</v>
       </c>
       <c r="Q38" s="24">
         <v>13</v>
@@ -3640,8 +3731,8 @@
       <c r="S38" s="24">
         <v>44</v>
       </c>
-      <c r="T38" s="29">
-        <v>3.56</v>
+      <c r="T38" s="39">
+        <v>3.55</v>
       </c>
       <c r="U38" s="24">
         <v>28.4</v>
@@ -3649,7 +3740,7 @@
       <c r="V38" s="24">
         <v>127</v>
       </c>
-      <c r="W38" s="29">
+      <c r="W38" s="39">
         <v>1.35</v>
       </c>
     </row>
@@ -3689,7 +3780,7 @@
       <c r="K39" s="24">
         <v>193</v>
       </c>
-      <c r="L39" s="29">
+      <c r="L39" s="39">
         <v>1.1100000000000001</v>
       </c>
       <c r="M39" s="24">
@@ -3701,8 +3792,8 @@
       <c r="O39" s="24">
         <v>3</v>
       </c>
-      <c r="P39" s="29">
-        <v>0.41</v>
+      <c r="P39" s="39">
+        <v>0.4</v>
       </c>
       <c r="Q39" s="24">
         <v>1.3</v>
@@ -3713,8 +3804,8 @@
       <c r="S39" s="24">
         <v>42</v>
       </c>
-      <c r="T39" s="29">
-        <v>3.65</v>
+      <c r="T39" s="39">
+        <v>3.73</v>
       </c>
       <c r="U39" s="24">
         <v>27.4</v>
@@ -3722,7 +3813,7 @@
       <c r="V39" s="24">
         <v>127</v>
       </c>
-      <c r="W39" s="29">
+      <c r="W39" s="39">
         <v>1.33</v>
       </c>
     </row>
@@ -3762,8 +3853,8 @@
       <c r="K40" s="24">
         <v>210</v>
       </c>
-      <c r="L40" s="29">
-        <v>1.39</v>
+      <c r="L40" s="39">
+        <v>1.38</v>
       </c>
       <c r="M40" s="24">
         <v>3.5</v>
@@ -3774,8 +3865,8 @@
       <c r="O40" s="24">
         <v>15</v>
       </c>
-      <c r="P40" s="29">
-        <v>0.97</v>
+      <c r="P40" s="39">
+        <v>0.99</v>
       </c>
       <c r="Q40" s="24">
         <v>3.6</v>
@@ -3786,8 +3877,8 @@
       <c r="S40" s="24">
         <v>61</v>
       </c>
-      <c r="T40" s="29">
-        <v>5.62</v>
+      <c r="T40" s="39">
+        <v>5.7</v>
       </c>
       <c r="U40" s="24">
         <v>29.3</v>
@@ -3795,7 +3886,7 @@
       <c r="V40" s="24">
         <v>153</v>
       </c>
-      <c r="W40" s="29">
+      <c r="W40" s="39">
         <v>1.74</v>
       </c>
     </row>
@@ -3827,8 +3918,8 @@
       <c r="K41" s="24">
         <v>1304</v>
       </c>
-      <c r="L41" s="29">
-        <v>1.1200000000000001</v>
+      <c r="L41" s="39">
+        <v>1.1000000000000001</v>
       </c>
       <c r="M41" s="24">
         <v>16.100000000000001</v>
@@ -3839,8 +3930,8 @@
       <c r="O41" s="24">
         <v>38</v>
       </c>
-      <c r="P41" s="29">
-        <v>0.75</v>
+      <c r="P41" s="39">
+        <v>0.77</v>
       </c>
       <c r="Q41" s="24">
         <v>7.2</v>
@@ -3851,7 +3942,7 @@
       <c r="S41" s="24">
         <v>396</v>
       </c>
-      <c r="T41" s="29">
+      <c r="T41" s="39">
         <v>4.13</v>
       </c>
       <c r="U41" s="24">
@@ -3860,8 +3951,8 @@
       <c r="V41" s="24">
         <v>838</v>
       </c>
-      <c r="W41" s="29">
-        <v>1.52</v>
+      <c r="W41" s="39">
+        <v>1.51</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -3901,6 +3992,9 @@
       <c r="K42" s="24">
         <v>166</v>
       </c>
+      <c r="L42" s="39">
+        <v>0.72</v>
+      </c>
       <c r="M42" s="24">
         <v>16.7</v>
       </c>
@@ -3910,6 +4004,9 @@
       <c r="O42" s="24">
         <v>18</v>
       </c>
+      <c r="P42" s="39">
+        <v>0.32</v>
+      </c>
       <c r="Q42" s="24">
         <v>9.8000000000000007</v>
       </c>
@@ -3919,11 +4016,17 @@
       <c r="S42" s="24">
         <v>56</v>
       </c>
-      <c r="U42" s="38">
+      <c r="T42" s="39">
+        <v>3.72</v>
+      </c>
+      <c r="U42" s="36">
         <v>23.9</v>
       </c>
-      <c r="V42" s="38">
+      <c r="V42" s="36">
         <v>142</v>
+      </c>
+      <c r="W42" s="39">
+        <v>1.45</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -3962,7 +4065,7 @@
       <c r="K43" s="24">
         <v>171</v>
       </c>
-      <c r="L43" s="29">
+      <c r="L43" s="39">
         <v>1.1200000000000001</v>
       </c>
       <c r="M43" s="24">
@@ -3974,7 +4077,7 @@
       <c r="O43" s="24">
         <v>10</v>
       </c>
-      <c r="P43" s="29">
+      <c r="P43" s="39">
         <v>0.56999999999999995</v>
       </c>
       <c r="Q43" s="24">
@@ -3986,7 +4089,7 @@
       <c r="S43" s="24">
         <v>61</v>
       </c>
-      <c r="T43" s="29">
+      <c r="T43" s="39">
         <v>3.76</v>
       </c>
       <c r="U43" s="24">
@@ -3995,7 +4098,7 @@
       <c r="V43" s="24">
         <v>120</v>
       </c>
-      <c r="W43" s="29">
+      <c r="W43" s="39">
         <v>1.41</v>
       </c>
     </row>
@@ -4035,7 +4138,7 @@
       <c r="K44" s="24">
         <v>201</v>
       </c>
-      <c r="L44" s="29">
+      <c r="L44" s="39">
         <v>1.1299999999999999</v>
       </c>
       <c r="M44" s="24">
@@ -4047,7 +4150,7 @@
       <c r="O44" s="24">
         <v>12</v>
       </c>
-      <c r="P44" s="29">
+      <c r="P44" s="39">
         <v>0.49</v>
       </c>
       <c r="Q44" s="24">
@@ -4059,7 +4162,7 @@
       <c r="S44" s="24">
         <v>61</v>
       </c>
-      <c r="T44" s="29">
+      <c r="T44" s="39">
         <v>4.2699999999999996</v>
       </c>
       <c r="U44" s="24">
@@ -4068,7 +4171,7 @@
       <c r="V44" s="24">
         <v>140</v>
       </c>
-      <c r="W44" s="29">
+      <c r="W44" s="39">
         <v>1.72</v>
       </c>
     </row>
@@ -4108,7 +4211,7 @@
       <c r="K45" s="24">
         <v>287</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="39">
         <v>1.28</v>
       </c>
       <c r="M45" s="24">
@@ -4120,7 +4223,7 @@
       <c r="O45" s="24">
         <v>12</v>
       </c>
-      <c r="P45" s="29">
+      <c r="P45" s="39">
         <v>1.5</v>
       </c>
       <c r="Q45" s="24">
@@ -4132,7 +4235,7 @@
       <c r="S45" s="24">
         <v>114</v>
       </c>
-      <c r="T45" s="29">
+      <c r="T45" s="39">
         <v>3.76</v>
       </c>
       <c r="U45" s="24">
@@ -4141,8 +4244,8 @@
       <c r="V45" s="24">
         <v>193</v>
       </c>
-      <c r="W45" s="29">
-        <v>1.72</v>
+      <c r="W45" s="39">
+        <v>1.73</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
@@ -4181,7 +4284,7 @@
       <c r="K46" s="24">
         <v>334</v>
       </c>
-      <c r="L46" s="29">
+      <c r="L46" s="39">
         <v>1.51</v>
       </c>
       <c r="M46" s="24">
@@ -4193,8 +4296,8 @@
       <c r="O46" s="24">
         <v>19</v>
       </c>
-      <c r="P46" s="29">
-        <v>1.1299999999999999</v>
+      <c r="P46" s="39">
+        <v>1.08</v>
       </c>
       <c r="Q46" s="24">
         <v>19.8</v>
@@ -4205,7 +4308,7 @@
       <c r="S46" s="24">
         <v>154</v>
       </c>
-      <c r="T46" s="29">
+      <c r="T46" s="39">
         <v>4.16</v>
       </c>
       <c r="U46" s="24">
@@ -4214,7 +4317,7 @@
       <c r="V46" s="24">
         <v>227</v>
       </c>
-      <c r="W46" s="29">
+      <c r="W46" s="39">
         <v>1.7</v>
       </c>
     </row>
@@ -4254,7 +4357,7 @@
       <c r="K47" s="24">
         <v>444</v>
       </c>
-      <c r="L47" s="29">
+      <c r="L47" s="39">
         <v>1.7</v>
       </c>
       <c r="M47" s="24">
@@ -4266,7 +4369,7 @@
       <c r="O47" s="24">
         <v>23</v>
       </c>
-      <c r="P47" s="29">
+      <c r="P47" s="39">
         <v>1.41</v>
       </c>
       <c r="Q47" s="24">
@@ -4278,8 +4381,8 @@
       <c r="S47" s="24">
         <v>206</v>
       </c>
-      <c r="T47" s="29">
-        <v>4.59</v>
+      <c r="T47" s="39">
+        <v>4.54</v>
       </c>
       <c r="U47" s="24">
         <v>27.5</v>
@@ -4287,8 +4390,8 @@
       <c r="V47" s="24">
         <v>287</v>
       </c>
-      <c r="W47" s="29">
-        <v>2.2200000000000002</v>
+      <c r="W47" s="39">
+        <v>2.23</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
@@ -4327,7 +4430,7 @@
       <c r="K48" s="24">
         <v>422</v>
       </c>
-      <c r="L48" s="29">
+      <c r="L48" s="39">
         <v>1.6</v>
       </c>
       <c r="M48" s="24">
@@ -4339,8 +4442,8 @@
       <c r="O48" s="24">
         <v>26</v>
       </c>
-      <c r="P48" s="29">
-        <v>1.03</v>
+      <c r="P48" s="39">
+        <v>1.04</v>
       </c>
       <c r="Q48" s="24">
         <v>10.5</v>
@@ -4351,8 +4454,8 @@
       <c r="S48" s="24">
         <v>199</v>
       </c>
-      <c r="T48" s="29">
-        <v>4.29</v>
+      <c r="T48" s="39">
+        <v>4.28</v>
       </c>
       <c r="U48" s="24">
         <v>32.5</v>
@@ -4360,8 +4463,8 @@
       <c r="V48" s="24">
         <v>310</v>
       </c>
-      <c r="W48" s="29">
-        <v>1.83</v>
+      <c r="W48" s="39">
+        <v>1.82</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
@@ -4400,7 +4503,7 @@
       <c r="K49" s="24">
         <v>430</v>
       </c>
-      <c r="L49" s="29">
+      <c r="L49" s="39">
         <v>1.52</v>
       </c>
       <c r="M49" s="24">
@@ -4412,8 +4515,8 @@
       <c r="O49" s="24">
         <v>20</v>
       </c>
-      <c r="P49" s="29">
-        <v>2.09</v>
+      <c r="P49" s="39">
+        <v>2.0699999999999998</v>
       </c>
       <c r="Q49" s="24">
         <v>18.8</v>
@@ -4424,8 +4527,8 @@
       <c r="S49" s="24">
         <v>168</v>
       </c>
-      <c r="T49" s="29">
-        <v>4.41</v>
+      <c r="T49" s="39">
+        <v>4.3899999999999997</v>
       </c>
       <c r="U49" s="24">
         <v>36.4</v>
@@ -4433,7 +4536,7 @@
       <c r="V49" s="24">
         <v>360</v>
       </c>
-      <c r="W49" s="29">
+      <c r="W49" s="39">
         <v>1.68</v>
       </c>
     </row>
@@ -4473,8 +4576,8 @@
       <c r="K50" s="24">
         <v>541</v>
       </c>
-      <c r="L50" s="29">
-        <v>1.22</v>
+      <c r="L50" s="39">
+        <v>1.24</v>
       </c>
       <c r="M50" s="24">
         <v>4.5999999999999996</v>
@@ -4485,8 +4588,8 @@
       <c r="O50" s="24">
         <v>41</v>
       </c>
-      <c r="P50" s="29">
-        <v>1.29</v>
+      <c r="P50" s="39">
+        <v>1.26</v>
       </c>
       <c r="Q50" s="24">
         <v>3.2</v>
@@ -4497,8 +4600,8 @@
       <c r="S50" s="24">
         <v>213</v>
       </c>
-      <c r="T50" s="29">
-        <v>4.79</v>
+      <c r="T50" s="39">
+        <v>4.67</v>
       </c>
       <c r="U50" s="24">
         <v>36.6</v>
@@ -4506,8 +4609,8 @@
       <c r="V50" s="24">
         <v>427</v>
       </c>
-      <c r="W50" s="29">
-        <v>1.36</v>
+      <c r="W50" s="39">
+        <v>1.37</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
@@ -4538,8 +4641,8 @@
       <c r="K51" s="24">
         <v>2996</v>
       </c>
-      <c r="L51" s="29">
-        <v>1.43</v>
+      <c r="L51" s="39">
+        <v>1.39</v>
       </c>
       <c r="M51" s="24">
         <v>21.5</v>
@@ -4550,8 +4653,8 @@
       <c r="O51" s="24">
         <v>181</v>
       </c>
-      <c r="P51" s="29">
-        <v>1.26</v>
+      <c r="P51" s="39">
+        <v>1.1499999999999999</v>
       </c>
       <c r="Q51" s="24">
         <v>13</v>
@@ -4562,8 +4665,8 @@
       <c r="S51" s="24">
         <v>1232</v>
       </c>
-      <c r="T51" s="29">
-        <v>4.33</v>
+      <c r="T51" s="39">
+        <v>4.2699999999999996</v>
       </c>
       <c r="U51" s="24">
         <v>29.3</v>
@@ -4571,8 +4674,8 @@
       <c r="V51" s="24">
         <v>2206</v>
       </c>
-      <c r="W51" s="29">
-        <v>1.71</v>
+      <c r="W51" s="39">
+        <v>1.69</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
@@ -4611,6 +4714,9 @@
       <c r="K52" s="24">
         <v>79</v>
       </c>
+      <c r="L52" s="39">
+        <v>0.99</v>
+      </c>
       <c r="M52" s="24">
         <v>26.8</v>
       </c>
@@ -4620,20 +4726,29 @@
       <c r="O52" s="24">
         <v>16</v>
       </c>
+      <c r="P52" s="39">
+        <v>0.74</v>
+      </c>
       <c r="Q52" s="24">
         <v>7.3</v>
       </c>
       <c r="R52" s="24">
         <v>5.3</v>
       </c>
-      <c r="S52" s="38">
+      <c r="S52" s="36">
         <v>23</v>
       </c>
-      <c r="U52" s="38">
+      <c r="T52" s="39">
+        <v>3.86</v>
+      </c>
+      <c r="U52" s="36">
         <v>19.899999999999999</v>
       </c>
-      <c r="V52" s="38">
+      <c r="V52" s="36">
         <v>57</v>
+      </c>
+      <c r="W52" s="39">
+        <v>1.48</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
@@ -4672,7 +4787,7 @@
       <c r="K53" s="24">
         <v>106</v>
       </c>
-      <c r="L53" s="29">
+      <c r="L53" s="39">
         <v>1.04</v>
       </c>
       <c r="M53" s="24">
@@ -4684,7 +4799,7 @@
       <c r="O53" s="24">
         <v>15</v>
       </c>
-      <c r="P53" s="29">
+      <c r="P53" s="39">
         <v>0.64</v>
       </c>
       <c r="Q53" s="24">
@@ -4696,7 +4811,7 @@
       <c r="S53" s="24">
         <v>43</v>
       </c>
-      <c r="T53" s="29">
+      <c r="T53" s="39">
         <v>3.93</v>
       </c>
       <c r="U53" s="24">
@@ -4705,7 +4820,7 @@
       <c r="V53" s="24">
         <v>79</v>
       </c>
-      <c r="W53" s="29">
+      <c r="W53" s="39">
         <v>1.92</v>
       </c>
     </row>
@@ -4745,7 +4860,7 @@
       <c r="K54" s="24">
         <v>160</v>
       </c>
-      <c r="L54" s="29">
+      <c r="L54" s="39">
         <v>1.1399999999999999</v>
       </c>
       <c r="M54" s="24">
@@ -4757,7 +4872,7 @@
       <c r="O54" s="24">
         <v>12</v>
       </c>
-      <c r="P54" s="29">
+      <c r="P54" s="39">
         <v>0.49</v>
       </c>
       <c r="Q54" s="24">
@@ -4769,7 +4884,7 @@
       <c r="S54" s="24">
         <v>58</v>
       </c>
-      <c r="T54" s="29">
+      <c r="T54" s="39">
         <v>3.97</v>
       </c>
       <c r="U54" s="24">
@@ -4778,7 +4893,7 @@
       <c r="V54" s="24">
         <v>117</v>
       </c>
-      <c r="W54" s="29">
+      <c r="W54" s="39">
         <v>1.9</v>
       </c>
     </row>
@@ -4818,7 +4933,7 @@
       <c r="K55" s="24">
         <v>319</v>
       </c>
-      <c r="L55" s="29">
+      <c r="L55" s="39">
         <v>2.02</v>
       </c>
       <c r="M55" s="24">
@@ -4830,7 +4945,7 @@
       <c r="O55" s="24">
         <v>7</v>
       </c>
-      <c r="P55" s="29">
+      <c r="P55" s="39">
         <v>0.88</v>
       </c>
       <c r="Q55" s="24">
@@ -4842,8 +4957,8 @@
       <c r="S55" s="24">
         <v>115</v>
       </c>
-      <c r="T55" s="29">
-        <v>5.41</v>
+      <c r="T55" s="39">
+        <v>5.38</v>
       </c>
       <c r="U55" s="24">
         <v>26.4</v>
@@ -4851,8 +4966,8 @@
       <c r="V55" s="24">
         <v>148</v>
       </c>
-      <c r="W55" s="29">
-        <v>2.0099999999999998</v>
+      <c r="W55" s="39">
+        <v>2.02</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
@@ -4891,7 +5006,7 @@
       <c r="K56" s="24">
         <v>522</v>
       </c>
-      <c r="L56" s="29">
+      <c r="L56" s="39">
         <v>2.77</v>
       </c>
       <c r="M56" s="24">
@@ -4903,7 +5018,7 @@
       <c r="O56" s="24">
         <v>18</v>
       </c>
-      <c r="P56" s="29">
+      <c r="P56" s="39">
         <v>3.91</v>
       </c>
       <c r="Q56" s="24">
@@ -4915,7 +5030,7 @@
       <c r="S56" s="24">
         <v>213</v>
       </c>
-      <c r="T56" s="29">
+      <c r="T56" s="39">
         <v>6.48</v>
       </c>
       <c r="U56" s="24">
@@ -4924,8 +5039,8 @@
       <c r="V56" s="24">
         <v>275</v>
       </c>
-      <c r="W56" s="29">
-        <v>3.84</v>
+      <c r="W56" s="39">
+        <v>3.83</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
@@ -4963,7 +5078,7 @@
       <c r="K57" s="24">
         <v>641</v>
       </c>
-      <c r="L57" s="29">
+      <c r="L57" s="39">
         <v>3.04</v>
       </c>
       <c r="M57" s="24">
@@ -4975,8 +5090,8 @@
       <c r="O57" s="24">
         <v>33</v>
       </c>
-      <c r="P57" s="29">
-        <v>11.82</v>
+      <c r="P57" s="39">
+        <v>11.8</v>
       </c>
       <c r="Q57" s="24">
         <v>143.1</v>
@@ -4987,8 +5102,8 @@
       <c r="S57" s="24">
         <v>264</v>
       </c>
-      <c r="T57" s="29">
-        <v>7.82</v>
+      <c r="T57" s="39">
+        <v>7.8</v>
       </c>
       <c r="U57" s="24">
         <v>35.4</v>
@@ -4996,7 +5111,7 @@
       <c r="V57" s="24">
         <v>333</v>
       </c>
-      <c r="W57" s="29">
+      <c r="W57" s="39">
         <v>4.53</v>
       </c>
     </row>
@@ -5036,7 +5151,7 @@
       <c r="K58" s="24">
         <v>533</v>
       </c>
-      <c r="L58" s="29">
+      <c r="L58" s="39">
         <v>2.86</v>
       </c>
       <c r="M58" s="24">
@@ -5048,8 +5163,8 @@
       <c r="O58" s="24">
         <v>15</v>
       </c>
-      <c r="P58" s="29">
-        <v>17.36</v>
+      <c r="P58" s="39">
+        <v>17.54</v>
       </c>
       <c r="Q58" s="24">
         <v>167.8</v>
@@ -5060,8 +5175,8 @@
       <c r="S58" s="24">
         <v>220</v>
       </c>
-      <c r="T58" s="29">
-        <v>7.18</v>
+      <c r="T58" s="39">
+        <v>7.25</v>
       </c>
       <c r="U58" s="24">
         <v>37.5</v>
@@ -5069,8 +5184,8 @@
       <c r="V58" s="24">
         <v>314</v>
       </c>
-      <c r="W58" s="29">
-        <v>3.81</v>
+      <c r="W58" s="39">
+        <v>3.82</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.3">
@@ -5109,8 +5224,8 @@
       <c r="K59" s="24">
         <v>487</v>
       </c>
-      <c r="L59" s="29">
-        <v>6.25</v>
+      <c r="L59" s="39">
+        <v>6.22</v>
       </c>
       <c r="M59" s="24">
         <v>39.9</v>
@@ -5121,8 +5236,8 @@
       <c r="O59" s="24">
         <v>15</v>
       </c>
-      <c r="P59" s="29">
-        <v>133.28</v>
+      <c r="P59" s="39">
+        <v>132.76</v>
       </c>
       <c r="Q59" s="24">
         <v>685.1</v>
@@ -5133,8 +5248,8 @@
       <c r="S59" s="24">
         <v>211</v>
       </c>
-      <c r="T59" s="29">
-        <v>19.47</v>
+      <c r="T59" s="39">
+        <v>19.600000000000001</v>
       </c>
       <c r="U59" s="24">
         <v>38.6</v>
@@ -5142,8 +5257,8 @@
       <c r="V59" s="24">
         <v>299</v>
       </c>
-      <c r="W59" s="29">
-        <v>9.51</v>
+      <c r="W59" s="39">
+        <v>9.4600000000000009</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.3">
@@ -5182,8 +5297,8 @@
       <c r="K60" s="24">
         <v>562</v>
       </c>
-      <c r="L60" s="29">
-        <v>3.31</v>
+      <c r="L60" s="39">
+        <v>3.36</v>
       </c>
       <c r="M60" s="24">
         <v>10.5</v>
@@ -5194,8 +5309,8 @@
       <c r="O60" s="24">
         <v>15</v>
       </c>
-      <c r="P60" s="29">
-        <v>48.63</v>
+      <c r="P60" s="39">
+        <v>51.34</v>
       </c>
       <c r="Q60" s="24">
         <v>115.4</v>
@@ -5206,8 +5321,8 @@
       <c r="S60" s="24">
         <v>262</v>
       </c>
-      <c r="T60" s="29">
-        <v>9.6199999999999992</v>
+      <c r="T60" s="39">
+        <v>9.9</v>
       </c>
       <c r="U60" s="24">
         <v>39.299999999999997</v>
@@ -5215,8 +5330,8 @@
       <c r="V60" s="24">
         <v>359</v>
       </c>
-      <c r="W60" s="29">
-        <v>4.68</v>
+      <c r="W60" s="39">
+        <v>4.76</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.3">
@@ -5247,8 +5362,8 @@
       <c r="K61" s="24">
         <v>3409</v>
       </c>
-      <c r="L61" s="29">
-        <v>3.23</v>
+      <c r="L61" s="39">
+        <v>3.18</v>
       </c>
       <c r="M61" s="24">
         <v>35.9</v>
@@ -5259,8 +5374,8 @@
       <c r="O61" s="24">
         <v>146</v>
       </c>
-      <c r="P61" s="29">
-        <v>26.7</v>
+      <c r="P61" s="39">
+        <v>24.1</v>
       </c>
       <c r="Q61" s="24">
         <v>143.9</v>
@@ -5271,8 +5386,8 @@
       <c r="S61" s="24">
         <v>1409</v>
       </c>
-      <c r="T61" s="29">
-        <v>8.9499999999999993</v>
+      <c r="T61" s="39">
+        <v>8.8800000000000008</v>
       </c>
       <c r="U61" s="24">
         <v>33.299999999999997</v>
@@ -5280,8 +5395,8 @@
       <c r="V61" s="24">
         <v>1981</v>
       </c>
-      <c r="W61" s="29">
-        <v>4.6500000000000004</v>
+      <c r="W61" s="39">
+        <v>4.57</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.3">
@@ -5320,6 +5435,9 @@
       <c r="K62" s="24">
         <v>409</v>
       </c>
+      <c r="L62" s="39">
+        <v>1.85</v>
+      </c>
       <c r="M62" s="24">
         <v>37</v>
       </c>
@@ -5329,20 +5447,29 @@
       <c r="O62" s="24">
         <v>39</v>
       </c>
+      <c r="P62" s="39">
+        <v>0.92</v>
+      </c>
       <c r="Q62" s="24">
         <v>18.600000000000001</v>
       </c>
       <c r="R62" s="24">
         <v>11.4</v>
       </c>
-      <c r="S62" s="38">
+      <c r="S62" s="36">
         <v>162</v>
       </c>
-      <c r="U62" s="38">
+      <c r="T62" s="39">
+        <v>5.98</v>
+      </c>
+      <c r="U62" s="36">
         <v>37.9</v>
       </c>
-      <c r="V62" s="38">
+      <c r="V62" s="36">
         <v>384</v>
+      </c>
+      <c r="W62" s="39">
+        <v>2.13</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.3">
@@ -5381,7 +5508,7 @@
       <c r="K63" s="24">
         <v>441</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="39">
         <v>1.66</v>
       </c>
       <c r="M63" s="24">
@@ -5393,7 +5520,7 @@
       <c r="O63" s="24">
         <v>28</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="39">
         <v>2.0499999999999998</v>
       </c>
       <c r="Q63" s="24">
@@ -5405,7 +5532,7 @@
       <c r="S63" s="24">
         <v>185</v>
       </c>
-      <c r="T63" s="32">
+      <c r="T63" s="39">
         <v>5.0599999999999996</v>
       </c>
       <c r="U63" s="24">
@@ -5414,7 +5541,7 @@
       <c r="V63" s="24">
         <v>371</v>
       </c>
-      <c r="W63" s="32">
+      <c r="W63" s="39">
         <v>2.12</v>
       </c>
     </row>
@@ -5454,7 +5581,7 @@
       <c r="K64" s="24">
         <v>530</v>
       </c>
-      <c r="L64" s="32">
+      <c r="L64" s="39">
         <v>1.56</v>
       </c>
       <c r="M64" s="24">
@@ -5466,7 +5593,7 @@
       <c r="O64" s="24">
         <v>27</v>
       </c>
-      <c r="P64" s="32">
+      <c r="P64" s="39">
         <v>1.69</v>
       </c>
       <c r="Q64" s="24">
@@ -5478,7 +5605,7 @@
       <c r="S64" s="24">
         <v>239</v>
       </c>
-      <c r="T64" s="32">
+      <c r="T64" s="39">
         <v>4.5199999999999996</v>
       </c>
       <c r="U64" s="24">
@@ -5487,7 +5614,7 @@
       <c r="V64" s="24">
         <v>432</v>
       </c>
-      <c r="W64" s="32">
+      <c r="W64" s="39">
         <v>1.96</v>
       </c>
     </row>
@@ -5527,7 +5654,7 @@
       <c r="K65" s="24">
         <v>625</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="39">
         <v>1.74</v>
       </c>
       <c r="M65" s="24">
@@ -5539,7 +5666,7 @@
       <c r="O65" s="24">
         <v>31</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="39">
         <v>1.63</v>
       </c>
       <c r="Q65" s="24">
@@ -5551,8 +5678,8 @@
       <c r="S65" s="24">
         <v>273</v>
       </c>
-      <c r="T65" s="32">
-        <v>4.7699999999999996</v>
+      <c r="T65" s="39">
+        <v>4.78</v>
       </c>
       <c r="U65" s="24">
         <v>37.799999999999997</v>
@@ -5560,7 +5687,7 @@
       <c r="V65" s="24">
         <v>501</v>
       </c>
-      <c r="W65" s="32">
+      <c r="W65" s="39">
         <v>1.98</v>
       </c>
     </row>
@@ -5600,7 +5727,7 @@
       <c r="K66" s="24">
         <v>673</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="39">
         <v>1.62</v>
       </c>
       <c r="M66" s="24">
@@ -5612,7 +5739,7 @@
       <c r="O66" s="24">
         <v>43</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="39">
         <v>1.53</v>
       </c>
       <c r="Q66" s="24">
@@ -5624,8 +5751,8 @@
       <c r="S66" s="24">
         <v>329</v>
       </c>
-      <c r="T66" s="32">
-        <v>4.57</v>
+      <c r="T66" s="39">
+        <v>4.5599999999999996</v>
       </c>
       <c r="U66" s="24">
         <v>41.6</v>
@@ -5633,7 +5760,7 @@
       <c r="V66" s="24">
         <v>615</v>
       </c>
-      <c r="W66" s="32">
+      <c r="W66" s="39">
         <v>2.0099999999999998</v>
       </c>
     </row>
@@ -5672,7 +5799,7 @@
       <c r="K67" s="24">
         <v>648</v>
       </c>
-      <c r="L67" s="32">
+      <c r="L67" s="39">
         <v>1.44</v>
       </c>
       <c r="M67" s="24">
@@ -5684,7 +5811,7 @@
       <c r="O67" s="24">
         <v>39</v>
       </c>
-      <c r="P67" s="32">
+      <c r="P67" s="39">
         <v>1.2</v>
       </c>
       <c r="Q67" s="24">
@@ -5696,8 +5823,8 @@
       <c r="S67" s="24">
         <v>321</v>
       </c>
-      <c r="T67" s="32">
-        <v>4.72</v>
+      <c r="T67" s="39">
+        <v>4.71</v>
       </c>
       <c r="U67" s="24">
         <v>40.1</v>
@@ -5705,7 +5832,7 @@
       <c r="V67" s="24">
         <v>588</v>
       </c>
-      <c r="W67" s="32">
+      <c r="W67" s="39">
         <v>2.06</v>
       </c>
     </row>
@@ -5745,7 +5872,7 @@
       <c r="K68" s="24">
         <v>704</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="39">
         <v>1.45</v>
       </c>
       <c r="M68" s="24">
@@ -5757,7 +5884,7 @@
       <c r="O68" s="24">
         <v>41</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="39">
         <v>1.28</v>
       </c>
       <c r="Q68" s="24">
@@ -5769,7 +5896,7 @@
       <c r="S68" s="24">
         <v>353</v>
       </c>
-      <c r="T68" s="32">
+      <c r="T68" s="39">
         <v>4.4400000000000004</v>
       </c>
       <c r="U68" s="24">
@@ -5778,7 +5905,7 @@
       <c r="V68" s="24">
         <v>612</v>
       </c>
-      <c r="W68" s="32">
+      <c r="W68" s="39">
         <v>2.09</v>
       </c>
     </row>
@@ -5818,7 +5945,7 @@
       <c r="K69" s="24">
         <v>699</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="39">
         <v>1.37</v>
       </c>
       <c r="M69" s="24">
@@ -5830,8 +5957,8 @@
       <c r="O69" s="24">
         <v>42</v>
       </c>
-      <c r="P69" s="32">
-        <v>1.59</v>
+      <c r="P69" s="39">
+        <v>1.58</v>
       </c>
       <c r="Q69" s="24">
         <v>11.9</v>
@@ -5842,8 +5969,8 @@
       <c r="S69" s="24">
         <v>356</v>
       </c>
-      <c r="T69" s="32">
-        <v>4.1399999999999997</v>
+      <c r="T69" s="39">
+        <v>4.1100000000000003</v>
       </c>
       <c r="U69" s="24">
         <v>43.9</v>
@@ -5851,8 +5978,8 @@
       <c r="V69" s="24">
         <v>637</v>
       </c>
-      <c r="W69" s="32">
-        <v>1.84</v>
+      <c r="W69" s="39">
+        <v>1.85</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.3">
@@ -5891,7 +6018,7 @@
       <c r="K70" s="24">
         <v>800</v>
       </c>
-      <c r="L70" s="32">
+      <c r="L70" s="39">
         <v>1.62</v>
       </c>
       <c r="M70" s="24">
@@ -5903,8 +6030,8 @@
       <c r="O70" s="24">
         <v>63</v>
       </c>
-      <c r="P70" s="32">
-        <v>1.47</v>
+      <c r="P70" s="39">
+        <v>1.41</v>
       </c>
       <c r="Q70" s="24">
         <v>4</v>
@@ -5915,8 +6042,8 @@
       <c r="S70" s="24">
         <v>393</v>
       </c>
-      <c r="T70" s="32">
-        <v>5.82</v>
+      <c r="T70" s="39">
+        <v>5.75</v>
       </c>
       <c r="U70" s="24">
         <v>43.8</v>
@@ -5924,8 +6051,8 @@
       <c r="V70" s="24">
         <v>740</v>
       </c>
-      <c r="W70" s="32">
-        <v>2.1</v>
+      <c r="W70" s="39">
+        <v>2.11</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.3">
@@ -5955,8 +6082,8 @@
       <c r="K71" s="24">
         <v>5529</v>
       </c>
-      <c r="L71" s="32">
-        <v>1.55</v>
+      <c r="L71" s="39">
+        <v>1.58</v>
       </c>
       <c r="M71" s="24">
         <v>26.1</v>
@@ -5967,8 +6094,8 @@
       <c r="O71" s="24">
         <v>353</v>
       </c>
-      <c r="P71" s="32">
-        <v>1.52</v>
+      <c r="P71" s="39">
+        <v>1.44</v>
       </c>
       <c r="Q71" s="24">
         <v>19.399999999999999</v>
@@ -5979,8 +6106,8 @@
       <c r="S71" s="24">
         <v>2611</v>
       </c>
-      <c r="T71" s="32">
-        <v>4.75</v>
+      <c r="T71" s="39">
+        <v>4.83</v>
       </c>
       <c r="U71" s="24">
         <v>40.9</v>
@@ -5988,8 +6115,8 @@
       <c r="V71" s="24">
         <v>4880</v>
       </c>
-      <c r="W71" s="32">
-        <v>2.02</v>
+      <c r="W71" s="39">
+        <v>2.0299999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -19175,15 +19302,15 @@
       <c r="B2" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>91</v>
+      <c r="C2" s="38" t="s">
+        <v>140</v>
       </c>
       <c r="D2" s="15"/>
       <c r="F2" s="16" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -19192,7 +19319,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
@@ -19200,7 +19327,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H3" s="9"/>
     </row>
@@ -19209,7 +19336,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -19217,7 +19344,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H4" s="9"/>
     </row>
@@ -19226,7 +19353,7 @@
         <v>74</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H5" s="9"/>
     </row>
@@ -19235,148 +19362,148 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
       <c r="F9" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
       <c r="F10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
       <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="12" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
       <c r="F12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="37" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
       <c r="F13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="F15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="K15" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="F16" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="I16" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17" spans="6:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="F17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="18" spans="6:9" ht="46.8" x14ac:dyDescent="0.3">
@@ -19384,18 +19511,18 @@
         <v>21</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="6:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="F19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -19424,10 +19551,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" t="s">
         <v>127</v>
-      </c>
-      <c r="C1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -19435,10 +19562,10 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
         <v>129</v>
-      </c>
-      <c r="C2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -19446,10 +19573,10 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
         <v>131</v>
-      </c>
-      <c r="C3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -19457,10 +19584,10 @@
         <v>44</v>
       </c>
       <c r="B4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" t="s">
         <v>133</v>
-      </c>
-      <c r="C4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -19468,10 +19595,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
         <v>135</v>
-      </c>
-      <c r="C5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -19479,10 +19606,10 @@
         <v>65</v>
       </c>
       <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
         <v>137</v>
-      </c>
-      <c r="C6" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -19490,10 +19617,10 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" t="s">
         <v>139</v>
-      </c>
-      <c r="C7" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/00 Raw data/研究量能統計 2017-2025.xlsx
+++ b/00 Raw data/研究量能統計 2017-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACD25F0-4153-4135-8982-5C7708C1059D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1678FC-41D2-4668-A4EF-9B6F3EFCD24F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="139">
   <si>
     <t>學校</t>
   </si>
@@ -333,9 +333,6 @@
     <t>期間</t>
   </si>
   <si>
-    <t>Scopus updated</t>
-  </si>
-  <si>
     <t>指標</t>
   </si>
   <si>
@@ -523,9 +520,6 @@
   </si>
   <si>
     <t>YUNTECH</t>
-  </si>
-  <si>
-    <t>2026.08.05</t>
   </si>
 </sst>
 </file>
@@ -19284,14 +19278,11 @@
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="H1" s="9"/>
     </row>
@@ -19300,17 +19291,15 @@
         <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>140</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C2" s="38"/>
       <c r="D2" s="15"/>
       <c r="F2" s="16" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -19319,7 +19308,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
@@ -19327,7 +19316,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H3" s="9"/>
     </row>
@@ -19336,7 +19325,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -19344,7 +19333,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H4" s="9"/>
     </row>
@@ -19353,7 +19342,7 @@
         <v>74</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H5" s="9"/>
     </row>
@@ -19362,41 +19351,41 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="37"/>
       <c r="C9" s="37"/>
@@ -19405,7 +19394,7 @@
         <v>75</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H9" s="9"/>
     </row>
@@ -19418,7 +19407,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
@@ -19430,10 +19419,10 @@
         <v>15</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
@@ -19445,12 +19434,12 @@
         <v>16</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="37"/>
       <c r="C13" s="37"/>
@@ -19459,51 +19448,51 @@
         <v>7</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="F15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="K15" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="F16" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="I16" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="17" spans="6:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="F17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="6:9" ht="46.8" x14ac:dyDescent="0.3">
@@ -19511,18 +19500,18 @@
         <v>21</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="6:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="F19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -19551,10 +19540,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
         <v>126</v>
-      </c>
-      <c r="C1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -19562,10 +19551,10 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" t="s">
         <v>128</v>
-      </c>
-      <c r="C2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -19573,10 +19562,10 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s">
         <v>130</v>
-      </c>
-      <c r="C3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -19584,10 +19573,10 @@
         <v>44</v>
       </c>
       <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
         <v>132</v>
-      </c>
-      <c r="C4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -19595,10 +19584,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" t="s">
         <v>134</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -19606,10 +19595,10 @@
         <v>65</v>
       </c>
       <c r="B6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" t="s">
         <v>136</v>
-      </c>
-      <c r="C6" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -19617,10 +19606,10 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" t="s">
         <v>138</v>
-      </c>
-      <c r="C7" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/00 Raw data/研究量能統計 2017-2025.xlsx
+++ b/00 Raw data/研究量能統計 2017-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171DFE1E-E4BA-4E0D-8657-303A91350BA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67D2DAE-CD25-4A3A-9DE0-87F020059F36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/00 Raw data/研究量能統計 2017-2025.xlsx
+++ b/00 Raw data/研究量能統計 2017-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67D2DAE-CD25-4A3A-9DE0-87F020059F36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E37AB1-9FAD-4982-B925-B6769CA61C7B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/00 Raw data/研究量能統計 2017-2025.xlsx
+++ b/00 Raw data/研究量能統計 2017-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E37AB1-9FAD-4982-B925-B6769CA61C7B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A0DB7-7173-4447-850C-BDC675B1392A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Scource" sheetId="5" r:id="rId2"/>
     <sheet name="Universities" sheetId="8" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">General!$A$1:$W$71</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -870,6 +873,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7A072E-3307-4539-A9D8-1310A9F473B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1074,15 +1131,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W71"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.8984375" style="5" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" style="24" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" style="24" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="16.69921875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="12.8984375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="17" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.8984375" style="12" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="17" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="18.796875" style="17" customWidth="1"/>
     <col min="8" max="8" width="12.19921875" style="26" customWidth="1"/>
     <col min="9" max="9" width="9.19921875" style="26" customWidth="1"/>
@@ -2490,7 +2548,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
@@ -2563,7 +2621,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>34</v>
       </c>
@@ -2636,7 +2694,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
@@ -2709,7 +2767,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>34</v>
       </c>
@@ -2782,7 +2840,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2855,7 +2913,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>34</v>
       </c>
@@ -2928,7 +2986,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>34</v>
       </c>
@@ -3001,7 +3059,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
@@ -3074,7 +3132,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
@@ -3147,7 +3205,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
@@ -3212,7 +3270,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>44</v>
       </c>
@@ -3285,7 +3343,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>44</v>
       </c>
@@ -3358,7 +3416,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>44</v>
       </c>
@@ -3431,7 +3489,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>44</v>
       </c>
@@ -3504,7 +3562,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>44</v>
       </c>
@@ -3577,7 +3635,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>44</v>
       </c>
@@ -3650,7 +3708,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>44</v>
       </c>
@@ -3723,7 +3781,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>44</v>
       </c>
@@ -3796,7 +3854,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>44</v>
       </c>
@@ -3869,7 +3927,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -6099,6 +6157,17 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W71" xr:uid="{07A6B285-2C99-482F-BAA7-77917DF2C52A}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="北科大"/>
+        <filter val="台灣"/>
+        <filter val="高科大"/>
+        <filter val="雲科大"/>
+        <filter val="臺科大"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/00 Raw data/研究量能統計 2017-2025.xlsx
+++ b/00 Raw data/研究量能統計 2017-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A0DB7-7173-4447-850C-BDC675B1392A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F48261-23DB-4BA4-8C64-D394AB8CCAF6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1138,11 +1138,11 @@
     <col min="1" max="1" width="8.8984375" style="5" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.8984375" style="24" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="16.69921875" style="26" customWidth="1"/>
+    <col min="4" max="4" width="16.69921875" style="26" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12.8984375" style="12" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="17" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.796875" style="17" customWidth="1"/>
-    <col min="8" max="8" width="12.19921875" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.796875" style="17" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.19921875" style="26" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.19921875" style="26" customWidth="1"/>
     <col min="10" max="10" width="20.8984375" style="26" customWidth="1"/>
     <col min="11" max="11" width="19" style="28" customWidth="1"/>
@@ -1888,7 +1888,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>33</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>52</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>59</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>65</v>
       </c>
@@ -6165,6 +6165,19 @@
         <filter val="高科大"/>
         <filter val="雲科大"/>
         <filter val="臺科大"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="2017"/>
+        <filter val="2018"/>
+        <filter val="2019"/>
+        <filter val="2020"/>
+        <filter val="2021"/>
+        <filter val="2022"/>
+        <filter val="2023"/>
+        <filter val="2024"/>
+        <filter val="2025"/>
       </filters>
     </filterColumn>
   </autoFilter>
